--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -2873,10 +2873,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121082250</v>
+        <v>121082474</v>
       </c>
       <c r="B23" t="n">
-        <v>91955</v>
+        <v>77530</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,34 +2889,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nordängesberget, Ly lm</t>
+          <t>Rackoliden, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607306</v>
+        <v>607272</v>
       </c>
       <c r="R23" t="n">
-        <v>7224137</v>
+        <v>7224171</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121082474</v>
+        <v>121082250</v>
       </c>
       <c r="B24" t="n">
-        <v>77530</v>
+        <v>91955</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2995,34 +2995,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rackoliden, Ly lm</t>
+          <t>Nordängesberget, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607272</v>
+        <v>607306</v>
       </c>
       <c r="R24" t="n">
-        <v>7224171</v>
+        <v>7224137</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -2131,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121066957</v>
+        <v>121066958</v>
       </c>
       <c r="B16" t="n">
-        <v>78334</v>
+        <v>79190</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607362</v>
+        <v>607359</v>
       </c>
       <c r="R16" t="n">
-        <v>7224148</v>
+        <v>7224158</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121066958</v>
+        <v>121066957</v>
       </c>
       <c r="B17" t="n">
-        <v>79187</v>
+        <v>78337</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607359</v>
+        <v>607362</v>
       </c>
       <c r="R17" t="n">
-        <v>7224158</v>
+        <v>7224148</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121082411</v>
+        <v>121082474</v>
       </c>
       <c r="B18" t="n">
-        <v>90841</v>
+        <v>77533</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2355,38 +2355,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nordängesberget, Ly lm</t>
+          <t>Rackoliden, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607311</v>
+        <v>607272</v>
       </c>
       <c r="R18" t="n">
-        <v>7224135</v>
+        <v>7224171</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121082146</v>
+        <v>121082263</v>
       </c>
       <c r="B19" t="n">
-        <v>79187</v>
+        <v>78338</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121082438</v>
+        <v>121082231</v>
       </c>
       <c r="B20" t="n">
-        <v>91963</v>
+        <v>91985</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2571,21 +2571,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607298</v>
+        <v>607299</v>
       </c>
       <c r="R20" t="n">
-        <v>7224151</v>
+        <v>7224162</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121082231</v>
+        <v>121082438</v>
       </c>
       <c r="B21" t="n">
-        <v>91975</v>
+        <v>91973</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607299</v>
+        <v>607298</v>
       </c>
       <c r="R21" t="n">
-        <v>7224162</v>
+        <v>7224151</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
         <v>121082483</v>
       </c>
       <c r="B22" t="n">
-        <v>77982</v>
+        <v>77985</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121082474</v>
+        <v>121082146</v>
       </c>
       <c r="B23" t="n">
-        <v>77530</v>
+        <v>79190</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,21 +2889,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2982,7 +2982,7 @@
         <v>121082250</v>
       </c>
       <c r="B24" t="n">
-        <v>91955</v>
+        <v>91965</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3085,10 +3085,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121082263</v>
+        <v>121082411</v>
       </c>
       <c r="B25" t="n">
-        <v>78335</v>
+        <v>90851</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,38 +3097,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rackoliden, Ly lm</t>
+          <t>Nordängesberget, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607272</v>
+        <v>607311</v>
       </c>
       <c r="R25" t="n">
-        <v>7224171</v>
+        <v>7224135</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -2767,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121082483</v>
+        <v>121082146</v>
       </c>
       <c r="B22" t="n">
-        <v>77985</v>
+        <v>79190</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,21 +2783,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121082146</v>
+        <v>121082483</v>
       </c>
       <c r="B23" t="n">
-        <v>79190</v>
+        <v>77985</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,21 +2889,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -2343,10 +2343,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121082474</v>
+        <v>121082483</v>
       </c>
       <c r="B18" t="n">
-        <v>77533</v>
+        <v>77985</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2359,21 +2359,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121082263</v>
+        <v>121082438</v>
       </c>
       <c r="B19" t="n">
-        <v>78338</v>
+        <v>91973</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,38 +2461,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rackoliden, Ly lm</t>
+          <t>Nordängesberget, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607272</v>
+        <v>607298</v>
       </c>
       <c r="R19" t="n">
-        <v>7224171</v>
+        <v>7224151</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121082231</v>
+        <v>121082146</v>
       </c>
       <c r="B20" t="n">
-        <v>91985</v>
+        <v>79190</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,38 +2567,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nordängesberget, Ly lm</t>
+          <t>Rackoliden, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607299</v>
+        <v>607272</v>
       </c>
       <c r="R20" t="n">
-        <v>7224162</v>
+        <v>7224171</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121082438</v>
+        <v>121082263</v>
       </c>
       <c r="B21" t="n">
-        <v>91973</v>
+        <v>78338</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2673,38 +2673,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nordängesberget, Ly lm</t>
+          <t>Rackoliden, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607298</v>
+        <v>607272</v>
       </c>
       <c r="R21" t="n">
-        <v>7224151</v>
+        <v>7224171</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121082146</v>
+        <v>121082474</v>
       </c>
       <c r="B22" t="n">
-        <v>79190</v>
+        <v>77533</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,21 +2783,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121082483</v>
+        <v>121082250</v>
       </c>
       <c r="B23" t="n">
-        <v>77985</v>
+        <v>91965</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,34 +2889,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rackoliden, Ly lm</t>
+          <t>Nordängesberget, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607272</v>
+        <v>607306</v>
       </c>
       <c r="R23" t="n">
-        <v>7224171</v>
+        <v>7224137</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121082250</v>
+        <v>121082411</v>
       </c>
       <c r="B24" t="n">
-        <v>91965</v>
+        <v>90851</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,25 +2991,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607306</v>
+        <v>607311</v>
       </c>
       <c r="R24" t="n">
-        <v>7224137</v>
+        <v>7224135</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,10 +3085,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121082411</v>
+        <v>121082231</v>
       </c>
       <c r="B25" t="n">
-        <v>90851</v>
+        <v>91985</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,25 +3097,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607311</v>
+        <v>607299</v>
       </c>
       <c r="R25" t="n">
-        <v>7224135</v>
+        <v>7224162</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -2134,7 +2134,7 @@
         <v>121066958</v>
       </c>
       <c r="B16" t="n">
-        <v>79190</v>
+        <v>79193</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>121066957</v>
       </c>
       <c r="B17" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121082483</v>
+        <v>121082474</v>
       </c>
       <c r="B18" t="n">
-        <v>77985</v>
+        <v>77536</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2359,21 +2359,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121082438</v>
+        <v>121082411</v>
       </c>
       <c r="B19" t="n">
-        <v>91973</v>
+        <v>90863</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,25 +2461,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607298</v>
+        <v>607311</v>
       </c>
       <c r="R19" t="n">
-        <v>7224151</v>
+        <v>7224135</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121082146</v>
+        <v>121082231</v>
       </c>
       <c r="B20" t="n">
-        <v>79190</v>
+        <v>91997</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,38 +2567,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rackoliden, Ly lm</t>
+          <t>Nordängesberget, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607272</v>
+        <v>607299</v>
       </c>
       <c r="R20" t="n">
-        <v>7224171</v>
+        <v>7224162</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121082263</v>
+        <v>121082483</v>
       </c>
       <c r="B21" t="n">
-        <v>78338</v>
+        <v>77988</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121082474</v>
+        <v>121082250</v>
       </c>
       <c r="B22" t="n">
-        <v>77533</v>
+        <v>91977</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,34 +2783,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rackoliden, Ly lm</t>
+          <t>Nordängesberget, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607272</v>
+        <v>607306</v>
       </c>
       <c r="R22" t="n">
-        <v>7224171</v>
+        <v>7224137</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121082250</v>
+        <v>121082438</v>
       </c>
       <c r="B23" t="n">
-        <v>91965</v>
+        <v>91985</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,25 +2885,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607306</v>
+        <v>607298</v>
       </c>
       <c r="R23" t="n">
-        <v>7224137</v>
+        <v>7224151</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121082411</v>
+        <v>121082263</v>
       </c>
       <c r="B24" t="n">
-        <v>90851</v>
+        <v>78341</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,38 +2991,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nordängesberget, Ly lm</t>
+          <t>Rackoliden, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607311</v>
+        <v>607272</v>
       </c>
       <c r="R24" t="n">
-        <v>7224135</v>
+        <v>7224171</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,10 +3085,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121082231</v>
+        <v>121082146</v>
       </c>
       <c r="B25" t="n">
-        <v>91985</v>
+        <v>79193</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,38 +3097,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nordängesberget, Ly lm</t>
+          <t>Rackoliden, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607299</v>
+        <v>607272</v>
       </c>
       <c r="R25" t="n">
-        <v>7224162</v>
+        <v>7224171</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -2343,10 +2343,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121082474</v>
+        <v>121082250</v>
       </c>
       <c r="B18" t="n">
-        <v>77536</v>
+        <v>91978</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6487</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rackoliden, Ly lm</t>
+          <t>Nordängesberget, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607272</v>
+        <v>607306</v>
       </c>
       <c r="R18" t="n">
-        <v>7224171</v>
+        <v>7224137</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121082411</v>
+        <v>121082474</v>
       </c>
       <c r="B19" t="n">
-        <v>90863</v>
+        <v>77536</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,38 +2461,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nordängesberget, Ly lm</t>
+          <t>Rackoliden, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607311</v>
+        <v>607272</v>
       </c>
       <c r="R19" t="n">
-        <v>7224135</v>
+        <v>7224171</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,7 +2558,7 @@
         <v>121082231</v>
       </c>
       <c r="B20" t="n">
-        <v>91997</v>
+        <v>91998</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121082483</v>
+        <v>121082438</v>
       </c>
       <c r="B21" t="n">
-        <v>77988</v>
+        <v>91986</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2673,38 +2673,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rackoliden, Ly lm</t>
+          <t>Nordängesberget, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607272</v>
+        <v>607298</v>
       </c>
       <c r="R21" t="n">
-        <v>7224171</v>
+        <v>7224151</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121082250</v>
+        <v>121082483</v>
       </c>
       <c r="B22" t="n">
-        <v>91977</v>
+        <v>77988</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,34 +2783,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nordängesberget, Ly lm</t>
+          <t>Rackoliden, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607306</v>
+        <v>607272</v>
       </c>
       <c r="R22" t="n">
-        <v>7224137</v>
+        <v>7224171</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121082438</v>
+        <v>121082263</v>
       </c>
       <c r="B23" t="n">
-        <v>91985</v>
+        <v>78341</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,38 +2885,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nordängesberget, Ly lm</t>
+          <t>Rackoliden, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607298</v>
+        <v>607272</v>
       </c>
       <c r="R23" t="n">
-        <v>7224151</v>
+        <v>7224171</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121082263</v>
+        <v>121082411</v>
       </c>
       <c r="B24" t="n">
-        <v>78341</v>
+        <v>90864</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,38 +2991,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rackoliden, Ly lm</t>
+          <t>Nordängesberget, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607272</v>
+        <v>607311</v>
       </c>
       <c r="R24" t="n">
-        <v>7224171</v>
+        <v>7224135</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3189,6 +3189,354 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124954596</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92309</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gunnarberg, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>607325</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7224167</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124954594</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90051</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gunnarberg, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>607287</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7224169</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124954592</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gunnarberg, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>607309</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7224127</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -3191,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124954596</v>
+        <v>124954592</v>
       </c>
       <c r="B26" t="n">
-        <v>92309</v>
+        <v>92293</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3203,25 +3203,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607325</v>
+        <v>607309</v>
       </c>
       <c r="R26" t="n">
-        <v>7224167</v>
+        <v>7224127</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124954592</v>
+        <v>124954596</v>
       </c>
       <c r="B28" t="n">
-        <v>92293</v>
+        <v>92309</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3435,25 +3435,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607309</v>
+        <v>607325</v>
       </c>
       <c r="R28" t="n">
-        <v>7224127</v>
+        <v>7224167</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -3191,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124954592</v>
+        <v>124954596</v>
       </c>
       <c r="B26" t="n">
-        <v>92293</v>
+        <v>92309</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3203,25 +3203,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607309</v>
+        <v>607325</v>
       </c>
       <c r="R26" t="n">
-        <v>7224127</v>
+        <v>7224167</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3307,10 +3307,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124954594</v>
+        <v>124954592</v>
       </c>
       <c r="B27" t="n">
-        <v>90051</v>
+        <v>92293</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3319,25 +3319,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607287</v>
+        <v>607309</v>
       </c>
       <c r="R27" t="n">
-        <v>7224169</v>
+        <v>7224127</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124954596</v>
+        <v>124954594</v>
       </c>
       <c r="B28" t="n">
-        <v>92309</v>
+        <v>90051</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3439,21 +3439,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607325</v>
+        <v>607287</v>
       </c>
       <c r="R28" t="n">
-        <v>7224167</v>
+        <v>7224169</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -3191,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124954596</v>
+        <v>124954592</v>
       </c>
       <c r="B26" t="n">
-        <v>92309</v>
+        <v>92293</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3203,25 +3203,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607325</v>
+        <v>607309</v>
       </c>
       <c r="R26" t="n">
-        <v>7224167</v>
+        <v>7224127</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3307,10 +3307,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124954592</v>
+        <v>124954596</v>
       </c>
       <c r="B27" t="n">
-        <v>92293</v>
+        <v>92309</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3319,25 +3319,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607309</v>
+        <v>607325</v>
       </c>
       <c r="R27" t="n">
-        <v>7224127</v>
+        <v>7224167</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -3191,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124954592</v>
+        <v>124954594</v>
       </c>
       <c r="B26" t="n">
-        <v>92293</v>
+        <v>90051</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3203,25 +3203,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607309</v>
+        <v>607287</v>
       </c>
       <c r="R26" t="n">
-        <v>7224127</v>
+        <v>7224169</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3307,10 +3307,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124954596</v>
+        <v>124954592</v>
       </c>
       <c r="B27" t="n">
-        <v>92309</v>
+        <v>92293</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3319,25 +3319,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607325</v>
+        <v>607309</v>
       </c>
       <c r="R27" t="n">
-        <v>7224167</v>
+        <v>7224127</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124954594</v>
+        <v>124954596</v>
       </c>
       <c r="B28" t="n">
-        <v>90051</v>
+        <v>92309</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3439,21 +3439,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607287</v>
+        <v>607325</v>
       </c>
       <c r="R28" t="n">
-        <v>7224169</v>
+        <v>7224167</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -3191,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124954594</v>
+        <v>124954596</v>
       </c>
       <c r="B26" t="n">
-        <v>90051</v>
+        <v>92309</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,21 +3207,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607287</v>
+        <v>607325</v>
       </c>
       <c r="R26" t="n">
-        <v>7224169</v>
+        <v>7224167</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124954596</v>
+        <v>124954594</v>
       </c>
       <c r="B28" t="n">
-        <v>92309</v>
+        <v>90051</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3439,21 +3439,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607325</v>
+        <v>607287</v>
       </c>
       <c r="R28" t="n">
-        <v>7224167</v>
+        <v>7224169</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -3191,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124954596</v>
+        <v>124954594</v>
       </c>
       <c r="B26" t="n">
-        <v>92309</v>
+        <v>90051</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,21 +3207,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607325</v>
+        <v>607287</v>
       </c>
       <c r="R26" t="n">
-        <v>7224167</v>
+        <v>7224169</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3307,10 +3307,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124954592</v>
+        <v>124954596</v>
       </c>
       <c r="B27" t="n">
-        <v>92293</v>
+        <v>92309</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3319,25 +3319,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607309</v>
+        <v>607325</v>
       </c>
       <c r="R27" t="n">
-        <v>7224127</v>
+        <v>7224167</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124954594</v>
+        <v>124954592</v>
       </c>
       <c r="B28" t="n">
-        <v>90051</v>
+        <v>92293</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3435,25 +3435,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607287</v>
+        <v>607309</v>
       </c>
       <c r="R28" t="n">
-        <v>7224169</v>
+        <v>7224127</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -3307,10 +3307,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124954596</v>
+        <v>124954592</v>
       </c>
       <c r="B27" t="n">
-        <v>92309</v>
+        <v>92293</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3319,25 +3319,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607325</v>
+        <v>607309</v>
       </c>
       <c r="R27" t="n">
-        <v>7224167</v>
+        <v>7224127</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124954592</v>
+        <v>124954596</v>
       </c>
       <c r="B28" t="n">
-        <v>92293</v>
+        <v>92309</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3435,25 +3435,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607309</v>
+        <v>607325</v>
       </c>
       <c r="R28" t="n">
-        <v>7224127</v>
+        <v>7224167</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -3307,10 +3307,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124954592</v>
+        <v>124954596</v>
       </c>
       <c r="B27" t="n">
-        <v>92293</v>
+        <v>92309</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3319,25 +3319,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607309</v>
+        <v>607325</v>
       </c>
       <c r="R27" t="n">
-        <v>7224127</v>
+        <v>7224167</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124954596</v>
+        <v>124954592</v>
       </c>
       <c r="B28" t="n">
-        <v>92309</v>
+        <v>92293</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3435,25 +3435,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607325</v>
+        <v>607309</v>
       </c>
       <c r="R28" t="n">
-        <v>7224167</v>
+        <v>7224127</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -3194,7 +3194,7 @@
         <v>124954594</v>
       </c>
       <c r="B26" t="n">
-        <v>90051</v>
+        <v>90204</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3307,10 +3307,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124954592</v>
+        <v>124954596</v>
       </c>
       <c r="B27" t="n">
-        <v>92293</v>
+        <v>92464</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3319,25 +3319,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607309</v>
+        <v>607325</v>
       </c>
       <c r="R27" t="n">
-        <v>7224127</v>
+        <v>7224167</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124954596</v>
+        <v>124954592</v>
       </c>
       <c r="B28" t="n">
-        <v>92309</v>
+        <v>92448</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3435,25 +3435,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607325</v>
+        <v>607309</v>
       </c>
       <c r="R28" t="n">
-        <v>7224167</v>
+        <v>7224127</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 46651-2019 artfynd.xlsx
+++ b/artfynd/A 46651-2019 artfynd.xlsx
@@ -3191,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124954594</v>
+        <v>124954592</v>
       </c>
       <c r="B26" t="n">
-        <v>90204</v>
+        <v>92448</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3203,25 +3203,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607287</v>
+        <v>607309</v>
       </c>
       <c r="R26" t="n">
-        <v>7224169</v>
+        <v>7224127</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124954592</v>
+        <v>124954594</v>
       </c>
       <c r="B28" t="n">
-        <v>92448</v>
+        <v>90204</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3435,25 +3435,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607309</v>
+        <v>607287</v>
       </c>
       <c r="R28" t="n">
-        <v>7224127</v>
+        <v>7224169</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
